--- a/diseases/d064/2026-2029.xlsx
+++ b/diseases/d064/2026-2029.xlsx
@@ -11989,12 +11989,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -12015,12 +12015,12 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -12063,40 +12063,181 @@
       </c>
       <c r="AV81" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW81" t="inlineStr">
+      <c r="AW82" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
+      <c r="AX82" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY81" t="inlineStr">
+      <c r="AY82" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
+      <c r="AZ82" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA81" t="inlineStr">
+      <c r="BA82" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB81" t="inlineStr">
+      <c r="BB82" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC81" t="inlineStr">
+      <c r="BC82" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -12218,7 +12359,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -12228,7 +12369,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d064/2026-2029.xlsx
+++ b/diseases/d064/2026-2029.xlsx
@@ -12243,6 +12243,147 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr"/>
+      <c r="AT83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12276,7 +12417,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12500,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -12369,7 +12510,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d064/2026-2029.xlsx
+++ b/diseases/d064/2026-2029.xlsx
@@ -11284,12 +11284,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -11358,42 +11358,42 @@
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11425,12 +11425,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -11451,7 +11451,7 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -11499,42 +11499,42 @@
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -11592,7 +11592,7 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -11733,7 +11733,7 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -11874,7 +11874,7 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -12015,7 +12015,7 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -12130,12 +12130,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -12156,12 +12156,12 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -12204,42 +12204,42 @@
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12271,12 +12271,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -12297,7 +12297,7 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -12345,40 +12345,322 @@
       </c>
       <c r="AV83" t="inlineStr">
         <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr"/>
+      <c r="AT84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV84" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW83" t="inlineStr">
+      <c r="AW84" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
+      <c r="AX84" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY83" t="inlineStr">
+      <c r="AY84" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
+      <c r="AZ84" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA83" t="inlineStr">
+      <c r="BA84" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB83" t="inlineStr">
+      <c r="BB84" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC83" t="inlineStr">
+      <c r="BC84" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr"/>
+      <c r="AT85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -12417,7 +12699,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -12500,7 +12782,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -12510,7 +12792,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d064/2026-2029.xlsx
+++ b/diseases/d064/2026-2029.xlsx
@@ -12666,6 +12666,288 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr"/>
+      <c r="AT86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV86" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC86" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr"/>
+      <c r="AT87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12699,7 +12981,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -12782,7 +13064,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -12792,7 +13074,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d064/2026-2029.xlsx
+++ b/diseases/d064/2026-2029.xlsx
@@ -12835,12 +12835,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -12861,12 +12861,12 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -12909,40 +12909,181 @@
       </c>
       <c r="AV87" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr"/>
+      <c r="AT88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW87" t="inlineStr">
+      <c r="AW88" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
+      <c r="AX88" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY87" t="inlineStr">
+      <c r="AY88" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
+      <c r="AZ88" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA87" t="inlineStr">
+      <c r="BA88" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB87" t="inlineStr">
+      <c r="BB88" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC87" t="inlineStr">
+      <c r="BC88" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -13064,7 +13205,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -13074,7 +13215,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d064/2026-2029.xlsx
+++ b/diseases/d064/2026-2029.xlsx
@@ -769,6 +769,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -910,6 +915,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1054,6 +1064,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1342,6 +1357,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1630,6 +1650,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1918,6 +1943,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2206,6 +2236,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2347,6 +2382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2488,6 +2528,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2776,6 +2821,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3064,6 +3114,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3352,6 +3407,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3640,6 +3700,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3781,6 +3846,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3922,6 +3992,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4210,6 +4285,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4498,6 +4578,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4786,6 +4871,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5074,6 +5164,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5215,6 +5310,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5356,6 +5456,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5644,6 +5749,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5932,6 +6042,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6220,6 +6335,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6508,6 +6628,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6649,6 +6774,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6790,6 +6920,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7078,6 +7213,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7366,6 +7506,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7654,6 +7799,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7942,6 +8092,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8230,6 +8385,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8371,6 +8531,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8512,6 +8677,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8794,6 +8964,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9076,6 +9251,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9358,6 +9538,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9640,6 +9825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9781,6 +9971,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9922,6 +10117,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10204,6 +10404,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10486,6 +10691,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10768,6 +10978,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11050,6 +11265,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11332,6 +11552,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11473,6 +11698,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12319,6 +12549,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13022,6 +13257,11 @@
       <c r="S88" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">

--- a/diseases/d064/2026-2029.xlsx
+++ b/diseases/d064/2026-2029.xlsx
@@ -13329,6 +13329,147 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr"/>
+      <c r="AT89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC89" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13362,7 +13503,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -13445,7 +13586,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -13455,7 +13596,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11">
